--- a/branches/fix/promis-29-scoring/StructureDefinition-mii-pr-pro-promis-29-social-function-tscore.xlsx
+++ b/branches/fix/promis-29-scoring/StructureDefinition-mii-pr-pro-promis-29-social-function-tscore.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-10-13T15:11:26+00:00</t>
+    <t>2026-10-14T06:32:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
